--- a/GRAMMAR/12_16_12.xlsx
+++ b/GRAMMAR/12_16_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C945EB9-1BF1-4CE1-A454-7C9D9E862495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD2F939-5835-4F9C-A4BB-2DF2EC3A8F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10560" yWindow="915" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19140" yWindow="1005" windowWidth="19260" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>Fre</t>
   </si>
@@ -300,6 +300,134 @@
   </si>
   <si>
     <t>原本应该，却…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さっき</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚才；方才</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必ずしも</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后接否定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>假如;决定；认为</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>だけでは</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光是…的话，后项多为负面评价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>てから</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动过先后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せっかく～のに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>明明却…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>どうも</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总觉得</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ことだった</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当时确实是…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>してる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反复…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>パリ発</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴黎发起的…(活动)/出发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ほとんどだった</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>占了绝大多数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あらゆる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有；一切；任何</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ながら</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一边...一边...；虽然...但是…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生まれだ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诞生的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今や</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在、如今。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界に届く</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传递给世界</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -694,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
@@ -1064,6 +1192,182 @@
       </c>
       <c r="C32" s="2" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A33" s="2">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A34" s="2">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A35" s="2">
+        <v>0</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A36" s="2">
+        <v>0</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A37" s="2">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A38" s="2">
+        <v>0</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A39" s="2">
+        <v>0</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A40" s="2">
+        <v>0</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A41" s="2">
+        <v>0</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A42" s="2">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A43" s="2">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A44" s="2">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A45" s="2">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A46" s="2">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A47" s="2">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A48" s="2">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
